--- a/economics/f1r3fly_sharding_economics.xlsx
+++ b/economics/f1r3fly_sharding_economics.xlsx
@@ -19,7 +19,8 @@
     <sheet name="Web 2.0" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="CAC" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="Connector" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="Summary" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Bandwidth" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Summary" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -117,6 +118,30 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Most assumption-sensitive figure; right for settlement events, bimodal in practice</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">OCI: first 10TB/mo free, then $0.0085/GB. Oracle reportedly moved to free egress across all regions in Feb 2026 - set to 0 to model that.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Third-party CDN / edge delivery, not covered by OCI free egress</t>
         </r>
       </text>
     </comment>
@@ -281,7 +306,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="299">
   <si>
     <t xml:space="preserve">F1R3FLY — Sharding Economics Model</t>
   </si>
@@ -448,6 +473,45 @@
     <t xml:space="preserve">Medical</t>
   </si>
   <si>
+    <t xml:space="preserve">BANDWIDTH (OCI egress; set to 0 to model reported free-egress)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internet egress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$/GB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inter-region egress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDN / edge egress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free egress tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEDIA PAYLOAD SIZES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radiology study (CT/MRI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audio, compressed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audio, lossless / hi-res</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radiology retrievals / patient-mo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rent — Monthly Network Cost of One Shard</t>
   </si>
   <si>
@@ -956,6 +1020,87 @@
   </si>
   <si>
     <t xml:space="preserve">Core connector rev/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bandwidth — Media Egress (the per-byte exception)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egress = payload size x moves x rate.  Negligible for text; dominant for imaging/lossless audio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARAMETERS (linked from Assumptions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internet egress ($/GB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDN / edge egress ($/GB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inter-region egress ($/GB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free egress tier (TB/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: first 10TB/mo free (per tenancy); Oracle reportedly moved to free egress across all regions Feb 2026. Figures below are marginal egress at scale (free tier negligible).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGRESS BY SCENARIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payload (MB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GB moved/mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egress @ internet ($/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egress @ CDN ($/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egress/payload ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of sector rev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radiology (medical imaging)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Music, compressed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Music, lossless / hi-res</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transactional (AI / fintech / EHR record)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">negligible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUSIC: BANDWIDTH-INCLUSIVE BREAK-EVEN FEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Music shard+compute cost ($/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break-even fee, compressed ($/play)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break-even fee, lossless ($/play)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current streaming fee ($/play)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: lossless exceeds the streaming fee -- needs a higher fee or edge caching.</t>
   </si>
   <si>
     <t xml:space="preserve">Summary — Five Sectors plus Web 2.0</t>
@@ -1064,7 +1209,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -1075,8 +1220,9 @@
     <numFmt numFmtId="171" formatCode="\$#,##0"/>
     <numFmt numFmtId="172" formatCode="0.00%"/>
     <numFmt numFmtId="173" formatCode="#,##0.0"/>
+    <numFmt numFmtId="174" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1208,6 +1354,13 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFD7263D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1275,7 +1428,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1353,6 +1506,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1453,6 +1610,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1738,7 +1903,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -2117,8 +2282,112 @@
         <v>52</v>
       </c>
     </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="20" t="n">
+        <v>0.0085</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B52" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A5:D5"/>
@@ -2126,6 +2395,8 @@
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A48:D48"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2156,7 +2427,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2168,7 +2439,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2180,7 +2451,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2192,59 +2463,59 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="B5" s="41" t="n">
+        <v>186</v>
+      </c>
+      <c r="B5" s="42" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="B6" s="41" t="n">
+        <v>187</v>
+      </c>
+      <c r="B6" s="42" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="B7" s="18" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>183</v>
+      <c r="A9" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="B10" s="41" t="n">
+        <v>197</v>
+      </c>
+      <c r="B10" s="42" t="n">
         <v>2000</v>
       </c>
       <c r="C10" s="18" t="n">
@@ -2261,20 +2532,20 @@
         <f aca="false">B10/E10</f>
         <v>0.02</v>
       </c>
-      <c r="G10" s="38" t="n">
+      <c r="G10" s="39" t="n">
         <f aca="false">$B$6/F10</f>
         <v>950</v>
       </c>
-      <c r="H10" s="38" t="n">
+      <c r="H10" s="39" t="n">
         <f aca="false">$B$5/F10</f>
         <v>2500</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="B11" s="41" t="n">
+        <v>198</v>
+      </c>
+      <c r="B11" s="42" t="n">
         <v>5000</v>
       </c>
       <c r="C11" s="18" t="n">
@@ -2291,20 +2562,20 @@
         <f aca="false">B11/E11</f>
         <v>0.1</v>
       </c>
-      <c r="G11" s="38" t="n">
+      <c r="G11" s="39" t="n">
         <f aca="false">$B$6/F11</f>
         <v>190</v>
       </c>
-      <c r="H11" s="38" t="n">
+      <c r="H11" s="39" t="n">
         <f aca="false">$B$5/F11</f>
         <v>500</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="B12" s="41" t="n">
+        <v>199</v>
+      </c>
+      <c r="B12" s="42" t="n">
         <v>10000</v>
       </c>
       <c r="C12" s="18" t="n">
@@ -2321,20 +2592,20 @@
         <f aca="false">B12/E12</f>
         <v>1</v>
       </c>
-      <c r="G12" s="38" t="n">
+      <c r="G12" s="39" t="n">
         <f aca="false">$B$6/F12</f>
         <v>19</v>
       </c>
-      <c r="H12" s="38" t="n">
+      <c r="H12" s="39" t="n">
         <f aca="false">$B$5/F12</f>
         <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="B13" s="41" t="n">
+        <v>200</v>
+      </c>
+      <c r="B13" s="42" t="n">
         <v>500000</v>
       </c>
       <c r="C13" s="18" t="n">
@@ -2351,20 +2622,20 @@
         <f aca="false">B13/E13</f>
         <v>0.5</v>
       </c>
-      <c r="G13" s="38" t="n">
+      <c r="G13" s="39" t="n">
         <f aca="false">$B$6/F13</f>
         <v>38</v>
       </c>
-      <c r="H13" s="38" t="n">
+      <c r="H13" s="39" t="n">
         <f aca="false">$B$5/F13</f>
         <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="B14" s="41" t="n">
+        <v>201</v>
+      </c>
+      <c r="B14" s="42" t="n">
         <v>5000000</v>
       </c>
       <c r="C14" s="18" t="n">
@@ -2381,20 +2652,20 @@
         <f aca="false">B14/E14</f>
         <v>0.686813186813187</v>
       </c>
-      <c r="G14" s="38" t="n">
+      <c r="G14" s="39" t="n">
         <f aca="false">$B$6/F14</f>
         <v>27.664</v>
       </c>
-      <c r="H14" s="38" t="n">
+      <c r="H14" s="39" t="n">
         <f aca="false">$B$5/F14</f>
         <v>72.8</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="B15" s="41" t="n">
+        <v>202</v>
+      </c>
+      <c r="B15" s="42" t="n">
         <v>20000000</v>
       </c>
       <c r="C15" s="18" t="n">
@@ -2411,18 +2682,18 @@
         <f aca="false">B15/E15</f>
         <v>2.74725274725275</v>
       </c>
-      <c r="G15" s="38" t="n">
+      <c r="G15" s="39" t="n">
         <f aca="false">$B$6/F15</f>
         <v>6.916</v>
       </c>
-      <c r="H15" s="38" t="n">
+      <c r="H15" s="39" t="n">
         <f aca="false">$B$5/F15</f>
         <v>18.2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -2433,34 +2704,34 @@
       <c r="H17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="E18" s="20" t="s">
+      <c r="A18" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="F18" s="20" t="s">
-        <v>195</v>
+      <c r="C18" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="B19" s="16" t="n">
         <f aca="false">F12</f>
         <v>1</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="23" t="n">
         <f aca="false">Music!$B$7*Music!$B$9</f>
         <v>0.003</v>
       </c>
@@ -2479,17 +2750,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="B20" s="16" t="n">
         <f aca="false">F14</f>
         <v>0.686813186813187</v>
       </c>
-      <c r="C20" s="39" t="n">
+      <c r="C20" s="40" t="n">
         <f aca="false">Assumptions!$B$31</f>
         <v>1</v>
       </c>
-      <c r="D20" s="40" t="n">
+      <c r="D20" s="41" t="n">
         <f aca="false">B20/C20</f>
         <v>0.686813186813187</v>
       </c>
@@ -2497,22 +2768,22 @@
         <f aca="false">B20/$B$7</f>
         <v>0.171703296703297</v>
       </c>
-      <c r="F20" s="40" t="n">
+      <c r="F20" s="41" t="n">
         <f aca="false">B20/(C20*$B$7)</f>
         <v>0.171703296703297</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="42" t="s">
-        <v>198</v>
-      </c>
-      <c r="B22" s="42"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
+      <c r="A22" s="43" t="s">
+        <v>211</v>
+      </c>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2549,7 +2820,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2557,7 +2828,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2565,7 +2836,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2573,7 +2844,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>0.005</v>
@@ -2581,7 +2852,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>0.2</v>
@@ -2589,7 +2860,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>0.0005</v>
@@ -2597,7 +2868,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>0.05</v>
@@ -2605,25 +2876,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="21" t="n">
+        <v>102</v>
+      </c>
+      <c r="B9" s="22" t="n">
         <f aca="false">Assumptions!$B$19</f>
         <v>30000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="36" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" s="37" t="n">
         <f aca="false">'Rent Cost Model'!$D$11</f>
         <v>4160.056</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -2631,61 +2902,61 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="B13" s="21" t="n">
+        <v>219</v>
+      </c>
+      <c r="B13" s="22" t="n">
         <f aca="false">AI!$C$19</f>
         <v>10000000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="B14" s="21" t="n">
+        <v>220</v>
+      </c>
+      <c r="B14" s="22" t="n">
         <f aca="false">Fintech!$B$18</f>
         <v>500000000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="B15" s="21" t="n">
+        <v>221</v>
+      </c>
+      <c r="B15" s="22" t="n">
         <f aca="false">Medical!$C$28</f>
         <v>364000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="B16" s="21" t="n">
+        <v>222</v>
+      </c>
+      <c r="B16" s="22" t="n">
         <f aca="false">Music!$B$8</f>
         <v>100000000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="B17" s="43" t="n">
+      <c r="A17" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="B17" s="44" t="n">
         <f aca="false">SUM(B13:B16)</f>
         <v>10964000000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="B18" s="21" t="n">
+        <v>224</v>
+      </c>
+      <c r="B18" s="22" t="n">
         <f aca="false">'Web 2.0'!$C$13+'Web 2.0'!$C$14+'Web 2.0'!$C$15</f>
         <v>7200000000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -2693,7 +2964,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="B21" s="14" t="n">
         <f aca="false">B17*B6</f>
@@ -2702,16 +2973,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="B22" s="23" t="n">
+        <v>227</v>
+      </c>
+      <c r="B22" s="24" t="n">
         <f aca="false">B21*B5</f>
         <v>10964000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B23" s="14" t="n">
         <f aca="false">B18*B8</f>
@@ -2720,25 +2991,25 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="B24" s="23" t="n">
+        <v>229</v>
+      </c>
+      <c r="B24" s="24" t="n">
         <f aca="false">B23*B7</f>
         <v>180000000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="B25" s="28" t="n">
+      <c r="A25" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="B25" s="29" t="n">
         <f aca="false">B22+B24</f>
         <v>190964000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="B26" s="14" t="n">
         <f aca="false">CEILING((B21+B23)/B9,1)</f>
@@ -2747,51 +3018,51 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="B27" s="23" t="n">
+        <v>232</v>
+      </c>
+      <c r="B27" s="24" t="n">
         <f aca="false">B26*B10</f>
         <v>50228516.144</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="B28" s="44" t="n">
+      <c r="A28" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="B28" s="45" t="n">
         <f aca="false">B25/B27</f>
         <v>3.80190407083749</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="D31" s="20"/>
+      <c r="A31" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="D31" s="21"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="32" t="n">
+      <c r="B32" s="33" t="n">
         <f aca="false">(A32-1)/A32</f>
         <v>0.5</v>
       </c>
-      <c r="C32" s="23" t="n">
+      <c r="C32" s="24" t="n">
         <f aca="false">$B$17*B32*$B$5</f>
         <v>27410000</v>
       </c>
@@ -2800,11 +3071,11 @@
       <c r="A33" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="B33" s="32" t="n">
+      <c r="B33" s="33" t="n">
         <f aca="false">(A33-1)/A33</f>
         <v>0.8</v>
       </c>
-      <c r="C33" s="23" t="n">
+      <c r="C33" s="24" t="n">
         <f aca="false">$B$17*B33*$B$5</f>
         <v>43856000</v>
       </c>
@@ -2813,11 +3084,11 @@
       <c r="A34" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="B34" s="32" t="n">
+      <c r="B34" s="33" t="n">
         <f aca="false">(A34-1)/A34</f>
         <v>0.9</v>
       </c>
-      <c r="C34" s="23" t="n">
+      <c r="C34" s="24" t="n">
         <f aca="false">$B$17*B34*$B$5</f>
         <v>49338000</v>
       </c>
@@ -2826,11 +3097,11 @@
       <c r="A35" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="B35" s="32" t="n">
+      <c r="B35" s="33" t="n">
         <f aca="false">(A35-1)/A35</f>
         <v>0.98</v>
       </c>
-      <c r="C35" s="23" t="n">
+      <c r="C35" s="24" t="n">
         <f aca="false">$B$17*B35*$B$5</f>
         <v>53723600</v>
       </c>
@@ -2839,11 +3110,11 @@
       <c r="A36" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="B36" s="32" t="n">
+      <c r="B36" s="33" t="n">
         <f aca="false">(A36-1)/A36</f>
         <v>0.99</v>
       </c>
-      <c r="C36" s="23" t="n">
+      <c r="C36" s="24" t="n">
         <f aca="false">$B$17*B36*$B$5</f>
         <v>54271800</v>
       </c>
@@ -2873,6 +3144,355 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" s="23" t="n">
+        <f aca="false">Assumptions!$B$43</f>
+        <v>0.0085</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B6" s="23" t="n">
+        <f aca="false">Assumptions!$B$45</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" s="23" t="n">
+        <f aca="false">Assumptions!$B$44</f>
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B8" s="22" t="n">
+        <f aca="false">Assumptions!$B$46</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B13" s="22" t="n">
+        <f aca="false">Assumptions!$B$49</f>
+        <v>250</v>
+      </c>
+      <c r="C13" s="22" t="n">
+        <f aca="false">Medical!$B$7*Assumptions!$B$52</f>
+        <v>36400000</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <f aca="false">C13*B13/1024</f>
+        <v>8886718.75</v>
+      </c>
+      <c r="E13" s="24" t="n">
+        <f aca="false">D13*$B$5</f>
+        <v>75537.109375</v>
+      </c>
+      <c r="F13" s="24" t="n">
+        <f aca="false">D13*$B$6</f>
+        <v>355468.75</v>
+      </c>
+      <c r="G13" s="35" t="n">
+        <f aca="false">E13/C13</f>
+        <v>0.0020751953125</v>
+      </c>
+      <c r="H13" s="33" t="n">
+        <f aca="false">E13/Medical!$F$28</f>
+        <v>0.0103759765625</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="B14" s="22" t="n">
+        <f aca="false">Assumptions!$B$50</f>
+        <v>4</v>
+      </c>
+      <c r="C14" s="22" t="n">
+        <f aca="false">Music!$B$8</f>
+        <v>100000000</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <f aca="false">C14*B14/1024</f>
+        <v>390625</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <f aca="false">D14*$B$5</f>
+        <v>3320.3125</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <f aca="false">D14*$B$6</f>
+        <v>15625</v>
+      </c>
+      <c r="G14" s="35" t="n">
+        <f aca="false">E14/C14</f>
+        <v>3.3203125E-005</v>
+      </c>
+      <c r="H14" s="33" t="n">
+        <f aca="false">E14/Music!$B$20</f>
+        <v>0.110677083333333</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B15" s="22" t="n">
+        <f aca="false">Assumptions!$B$51</f>
+        <v>40</v>
+      </c>
+      <c r="C15" s="22" t="n">
+        <f aca="false">Music!$B$8</f>
+        <v>100000000</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <f aca="false">C15*B15/1024</f>
+        <v>3906250</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <f aca="false">D15*$B$5</f>
+        <v>33203.125</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <f aca="false">D15*$B$6</f>
+        <v>156250</v>
+      </c>
+      <c r="G15" s="35" t="n">
+        <f aca="false">E15/C15</f>
+        <v>0.00033203125</v>
+      </c>
+      <c r="H15" s="33" t="n">
+        <f aca="false">E15/Music!$B$20</f>
+        <v>1.10677083333333</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="B16" s="46" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="C16" s="22" t="n">
+        <f aca="false">AI!$C$19</f>
+        <v>10000000000</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <f aca="false">C16*B16/1024</f>
+        <v>29296.875</v>
+      </c>
+      <c r="E16" s="24" t="n">
+        <f aca="false">D16*$B$5</f>
+        <v>249.0234375</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <f aca="false">D16*$B$6</f>
+        <v>1171.875</v>
+      </c>
+      <c r="G16" s="35" t="n">
+        <f aca="false">E16/C16</f>
+        <v>2.490234375E-008</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="B19" s="37" t="n">
+        <f aca="false">Music!$B$13</f>
+        <v>16640.224</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B20" s="35" t="n">
+        <f aca="false">(B19+E14)/C14</f>
+        <v>0.000199605365</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="B21" s="35" t="n">
+        <f aca="false">(B19+E15)/C15</f>
+        <v>0.00049843349</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="B22" s="32" t="n">
+        <f aca="false">Assumptions!$B$30</f>
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="47" t="s">
+        <v>264</v>
+      </c>
+      <c r="B23" s="47"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A23:H23"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -2886,7 +3506,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>265</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2896,7 +3516,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>226</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2905,151 +3525,151 @@
       <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>232</v>
+      <c r="A4" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="25" t="s">
         <v>41</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>233</v>
+        <v>273</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>234</v>
+        <v>274</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="E5" s="45" t="n">
+        <v>275</v>
+      </c>
+      <c r="E5" s="48" t="n">
         <f aca="false">AI!$B$12</f>
         <v>0.016640224</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>236</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="25" t="s">
         <v>43</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>237</v>
+        <v>277</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>238</v>
+        <v>278</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="E6" s="45" t="n">
+        <v>279</v>
+      </c>
+      <c r="E6" s="48" t="n">
         <f aca="false">Fintech!$B$11</f>
         <v>0.002080028</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>240</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="25" t="s">
         <v>54</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>241</v>
+        <v>281</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="E7" s="45" t="n">
+        <v>283</v>
+      </c>
+      <c r="E7" s="48" t="n">
         <f aca="false">Medical!$B$16</f>
         <v>0.04160056</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>244</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="25" t="s">
         <v>44</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>245</v>
+        <v>285</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>246</v>
+        <v>286</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>248</v>
+        <v>287</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>288</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>249</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>250</v>
+      <c r="A9" s="25" t="s">
+        <v>290</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>251</v>
+        <v>291</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>234</v>
+        <v>274</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="E9" s="37" t="s">
-        <v>253</v>
+        <v>292</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>293</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>254</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>256</v>
-      </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
+      <c r="A12" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>296</v>
+      </c>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="B14" s="46" t="s">
-        <v>258</v>
-      </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
+      <c r="A14" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="B14" s="49" t="s">
+        <v>298</v>
+      </c>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3084,7 +3704,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3092,96 +3712,96 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>60</v>
+      <c r="A4" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="21" t="n">
+        <v>74</v>
+      </c>
+      <c r="B5" s="22" t="n">
         <f aca="false">Assumptions!$B$6*Assumptions!$B$7</f>
         <v>160</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="23" t="n">
         <f aca="false">Assumptions!$B$11</f>
         <v>0.025</v>
       </c>
-      <c r="D5" s="23" t="n">
+      <c r="D5" s="24" t="n">
         <f aca="false">B5*C5*Assumptions!$B$10</f>
         <v>2920</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="B6" s="22" t="n">
         <f aca="false">Assumptions!$B$6*Assumptions!$B$8</f>
         <v>160</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <f aca="false">Assumptions!$B$12</f>
         <v>0.0015</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="24" t="n">
         <f aca="false">B6*C6*Assumptions!$B$10</f>
         <v>175.2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="21" t="n">
+        <v>76</v>
+      </c>
+      <c r="B7" s="22" t="n">
         <f aca="false">Assumptions!$B$6*Assumptions!$B$9*1024</f>
         <v>20480</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <f aca="false">Assumptions!$B$13</f>
         <v>0.0255</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="24" t="n">
         <f aca="false">B7*C7</f>
         <v>522.24</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="21" t="n">
+        <v>77</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="25" t="n">
+      <c r="A9" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="26" t="n">
         <f aca="false">SUM(D5:D8)</f>
         <v>3617.44</v>
       </c>
@@ -3190,29 +3810,29 @@
       <c r="A10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="26" t="n">
+      <c r="C10" s="27" t="n">
         <f aca="false">Assumptions!$B$14</f>
         <v>0.15</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="24" t="n">
         <f aca="false">D9*C10</f>
         <v>542.616</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="28" t="n">
+      <c r="A11" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="29" t="n">
         <f aca="false">D9+D10</f>
         <v>4160.056</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="29" t="n">
+      <c r="A13" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="30" t="n">
         <f aca="false">D11/Assumptions!$B$19</f>
         <v>0.000138668533333333</v>
       </c>
@@ -3248,7 +3868,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3256,24 +3876,24 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>73</v>
+      <c r="A4" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3284,11 +3904,11 @@
         <f aca="false">A5*30*Assumptions!$B$16</f>
         <v>15000</v>
       </c>
-      <c r="C5" s="30" t="n">
+      <c r="C5" s="31" t="n">
         <f aca="false">B5/Assumptions!$B$21</f>
         <v>9.375E-005</v>
       </c>
-      <c r="D5" s="31" t="n">
+      <c r="D5" s="32" t="n">
         <f aca="false">'Rent Cost Model'!$D$11/B5</f>
         <v>0.277337066666667</v>
       </c>
@@ -3301,11 +3921,11 @@
         <f aca="false">A6*30*Assumptions!$B$16</f>
         <v>150000</v>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="31" t="n">
         <f aca="false">B6/Assumptions!$B$21</f>
         <v>0.0009375</v>
       </c>
-      <c r="D6" s="31" t="n">
+      <c r="D6" s="32" t="n">
         <f aca="false">'Rent Cost Model'!$D$11/B6</f>
         <v>0.0277337066666667</v>
       </c>
@@ -3318,11 +3938,11 @@
         <f aca="false">A7*30*Assumptions!$B$16</f>
         <v>1500000</v>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="31" t="n">
         <f aca="false">B7/Assumptions!$B$21</f>
         <v>0.009375</v>
       </c>
-      <c r="D7" s="31" t="n">
+      <c r="D7" s="32" t="n">
         <f aca="false">'Rent Cost Model'!$D$11/B7</f>
         <v>0.00277337066666667</v>
       </c>
@@ -3335,11 +3955,11 @@
         <f aca="false">A8*30*Assumptions!$B$16</f>
         <v>15000000</v>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="31" t="n">
         <f aca="false">B8/Assumptions!$B$21</f>
         <v>0.09375</v>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="32" t="n">
         <f aca="false">'Rent Cost Model'!$D$11/B8</f>
         <v>0.000277337066666667</v>
       </c>
@@ -3352,18 +3972,18 @@
         <f aca="false">A9*30*Assumptions!$B$16</f>
         <v>150000000</v>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="31" t="n">
         <f aca="false">B9/Assumptions!$B$21</f>
         <v>0.9375</v>
       </c>
-      <c r="D9" s="31" t="n">
+      <c r="D9" s="32" t="n">
         <f aca="false">'Rent Cost Model'!$D$11/B9</f>
         <v>2.77337066666667E-005</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -3371,7 +3991,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>50</v>
@@ -3379,16 +3999,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B13" s="32" t="n">
+        <v>89</v>
+      </c>
+      <c r="B13" s="33" t="n">
         <f aca="false">1-1/B12</f>
         <v>0.98</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="B14" s="18" t="n">
         <v>1</v>
@@ -3396,9 +4016,9 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="32" t="n">
+        <v>91</v>
+      </c>
+      <c r="B15" s="33" t="n">
         <f aca="false">1-0.5*EXP(-B12/B14)</f>
         <v>1</v>
       </c>
@@ -3434,7 +4054,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3444,7 +4064,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3453,22 +4073,22 @@
       <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="33" t="n">
+      <c r="A4" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="33" t="n">
+      <c r="C4" s="34" t="n">
         <v>0.0001</v>
       </c>
-      <c r="D4" s="33" t="n">
+      <c r="D4" s="34" t="n">
         <v>0.001</v>
       </c>
-      <c r="E4" s="33" t="n">
+      <c r="E4" s="34" t="n">
         <v>0.01</v>
       </c>
-      <c r="F4" s="33" t="n">
+      <c r="F4" s="34" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3476,23 +4096,23 @@
       <c r="A5" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="B5" s="34" t="n">
+      <c r="B5" s="35" t="n">
         <f aca="false">'Rent Density'!$D$5-B$4</f>
         <v>0.277337066666667</v>
       </c>
-      <c r="C5" s="34" t="n">
+      <c r="C5" s="35" t="n">
         <f aca="false">'Rent Density'!$D$5-C$4</f>
         <v>0.277237066666667</v>
       </c>
-      <c r="D5" s="34" t="n">
+      <c r="D5" s="35" t="n">
         <f aca="false">'Rent Density'!$D$5-D$4</f>
         <v>0.276337066666667</v>
       </c>
-      <c r="E5" s="34" t="n">
+      <c r="E5" s="35" t="n">
         <f aca="false">'Rent Density'!$D$5-E$4</f>
         <v>0.267337066666667</v>
       </c>
-      <c r="F5" s="34" t="n">
+      <c r="F5" s="35" t="n">
         <f aca="false">'Rent Density'!$D$5-F$4</f>
         <v>0.177337066666667</v>
       </c>
@@ -3501,23 +4121,23 @@
       <c r="A6" s="18" t="n">
         <v>1000</v>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="35" t="n">
         <f aca="false">'Rent Density'!$D$6-B$4</f>
         <v>0.0277337066666667</v>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C6" s="35" t="n">
         <f aca="false">'Rent Density'!$D$6-C$4</f>
         <v>0.0276337066666667</v>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D6" s="35" t="n">
         <f aca="false">'Rent Density'!$D$6-D$4</f>
         <v>0.0267337066666667</v>
       </c>
-      <c r="E6" s="34" t="n">
+      <c r="E6" s="35" t="n">
         <f aca="false">'Rent Density'!$D$6-E$4</f>
         <v>0.0177337066666667</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="35" t="n">
         <f aca="false">'Rent Density'!$D$6-F$4</f>
         <v>-0.0722662933333333</v>
       </c>
@@ -3526,23 +4146,23 @@
       <c r="A7" s="18" t="n">
         <v>10000</v>
       </c>
-      <c r="B7" s="34" t="n">
+      <c r="B7" s="35" t="n">
         <f aca="false">'Rent Density'!$D$7-B$4</f>
         <v>0.00277337066666667</v>
       </c>
-      <c r="C7" s="34" t="n">
+      <c r="C7" s="35" t="n">
         <f aca="false">'Rent Density'!$D$7-C$4</f>
         <v>0.00267337066666667</v>
       </c>
-      <c r="D7" s="34" t="n">
+      <c r="D7" s="35" t="n">
         <f aca="false">'Rent Density'!$D$7-D$4</f>
         <v>0.00177337066666667</v>
       </c>
-      <c r="E7" s="34" t="n">
+      <c r="E7" s="35" t="n">
         <f aca="false">'Rent Density'!$D$7-E$4</f>
         <v>-0.00722662933333333</v>
       </c>
-      <c r="F7" s="34" t="n">
+      <c r="F7" s="35" t="n">
         <f aca="false">'Rent Density'!$D$7-F$4</f>
         <v>-0.0972266293333333</v>
       </c>
@@ -3551,23 +4171,23 @@
       <c r="A8" s="18" t="n">
         <v>100000</v>
       </c>
-      <c r="B8" s="34" t="n">
+      <c r="B8" s="35" t="n">
         <f aca="false">'Rent Density'!$D$8-B$4</f>
         <v>0.000277337066666667</v>
       </c>
-      <c r="C8" s="34" t="n">
+      <c r="C8" s="35" t="n">
         <f aca="false">'Rent Density'!$D$8-C$4</f>
         <v>0.000177337066666667</v>
       </c>
-      <c r="D8" s="34" t="n">
+      <c r="D8" s="35" t="n">
         <f aca="false">'Rent Density'!$D$8-D$4</f>
         <v>-0.000722662933333333</v>
       </c>
-      <c r="E8" s="34" t="n">
+      <c r="E8" s="35" t="n">
         <f aca="false">'Rent Density'!$D$8-E$4</f>
         <v>-0.00972266293333333</v>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F8" s="35" t="n">
         <f aca="false">'Rent Density'!$D$8-F$4</f>
         <v>-0.0997226629333333</v>
       </c>
@@ -3576,23 +4196,23 @@
       <c r="A9" s="18" t="n">
         <v>1000000</v>
       </c>
-      <c r="B9" s="34" t="n">
+      <c r="B9" s="35" t="n">
         <f aca="false">'Rent Density'!$D$9-B$4</f>
         <v>2.77337066666667E-005</v>
       </c>
-      <c r="C9" s="34" t="n">
+      <c r="C9" s="35" t="n">
         <f aca="false">'Rent Density'!$D$9-C$4</f>
         <v>-7.22662933333334E-005</v>
       </c>
-      <c r="D9" s="34" t="n">
+      <c r="D9" s="35" t="n">
         <f aca="false">'Rent Density'!$D$9-D$4</f>
         <v>-0.000972266293333333</v>
       </c>
-      <c r="E9" s="34" t="n">
+      <c r="E9" s="35" t="n">
         <f aca="false">'Rent Density'!$D$9-E$4</f>
         <v>-0.00997226629333333</v>
       </c>
-      <c r="F9" s="34" t="n">
+      <c r="F9" s="35" t="n">
         <f aca="false">'Rent Density'!$D$9-F$4</f>
         <v>-0.0999722662933333</v>
       </c>
@@ -3637,7 +4257,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3648,7 +4268,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3659,7 +4279,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -3670,52 +4290,52 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="22" t="n">
+        <v>98</v>
+      </c>
+      <c r="B5" s="23" t="n">
         <f aca="false">Assumptions!$B$28</f>
         <v>0.01</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="35" t="n">
+        <v>99</v>
+      </c>
+      <c r="B6" s="36" t="n">
         <f aca="false">Assumptions!$B$36</f>
         <v>1.2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="36" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" s="37" t="n">
         <f aca="false">'Rent Cost Model'!$D$11</f>
         <v>4160.056</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="23" t="n">
+        <v>101</v>
+      </c>
+      <c r="B8" s="24" t="n">
         <f aca="false">B6*B7</f>
         <v>4992.0672</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="21" t="n">
+        <v>102</v>
+      </c>
+      <c r="B9" s="22" t="n">
         <f aca="false">Assumptions!$B$19</f>
         <v>30000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>10000</v>
@@ -3723,7 +4343,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B11" s="14" t="n">
         <f aca="false">B8/B5</f>
@@ -3732,39 +4352,39 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B12" s="30" t="n">
+        <v>105</v>
+      </c>
+      <c r="B12" s="31" t="n">
         <f aca="false">B11/B9</f>
         <v>0.016640224</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>99</v>
+      <c r="A14" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37" t="s">
-        <v>100</v>
+      <c r="A15" s="38" t="s">
+        <v>113</v>
       </c>
       <c r="B15" s="18" t="n">
         <v>100</v>
@@ -3777,22 +4397,22 @@
         <f aca="false">CEILING(C15/$B$9,1)</f>
         <v>1</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="24" t="n">
         <f aca="false">D15*$B$8</f>
         <v>4992.0672</v>
       </c>
-      <c r="F15" s="23" t="n">
+      <c r="F15" s="24" t="n">
         <f aca="false">C15*$B$5</f>
         <v>10000</v>
       </c>
-      <c r="G15" s="38" t="n">
+      <c r="G15" s="39" t="n">
         <f aca="false">F15/E15</f>
         <v>2.00317816234525</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="37" t="s">
-        <v>101</v>
+      <c r="A16" s="38" t="s">
+        <v>114</v>
       </c>
       <c r="B16" s="18" t="n">
         <v>1000</v>
@@ -3805,22 +4425,22 @@
         <f aca="false">CEILING(C16/$B$9,1)</f>
         <v>1</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="24" t="n">
         <f aca="false">D16*$B$8</f>
         <v>4992.0672</v>
       </c>
-      <c r="F16" s="23" t="n">
+      <c r="F16" s="24" t="n">
         <f aca="false">C16*$B$5</f>
         <v>100000</v>
       </c>
-      <c r="G16" s="38" t="n">
+      <c r="G16" s="39" t="n">
         <f aca="false">F16/E16</f>
         <v>20.0317816234525</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="37" t="s">
-        <v>102</v>
+      <c r="A17" s="38" t="s">
+        <v>115</v>
       </c>
       <c r="B17" s="18" t="n">
         <v>10000</v>
@@ -3833,22 +4453,22 @@
         <f aca="false">CEILING(C17/$B$9,1)</f>
         <v>4</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="24" t="n">
         <f aca="false">D17*$B$8</f>
         <v>19968.2688</v>
       </c>
-      <c r="F17" s="23" t="n">
+      <c r="F17" s="24" t="n">
         <f aca="false">C17*$B$5</f>
         <v>1000000</v>
       </c>
-      <c r="G17" s="38" t="n">
+      <c r="G17" s="39" t="n">
         <f aca="false">F17/E17</f>
         <v>50.0794540586313</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="37" t="s">
-        <v>103</v>
+      <c r="A18" s="38" t="s">
+        <v>116</v>
       </c>
       <c r="B18" s="18" t="n">
         <v>100000</v>
@@ -3861,22 +4481,22 @@
         <f aca="false">CEILING(C18/$B$9,1)</f>
         <v>34</v>
       </c>
-      <c r="E18" s="23" t="n">
+      <c r="E18" s="24" t="n">
         <f aca="false">D18*$B$8</f>
         <v>169730.2848</v>
       </c>
-      <c r="F18" s="23" t="n">
+      <c r="F18" s="24" t="n">
         <f aca="false">C18*$B$5</f>
         <v>10000000</v>
       </c>
-      <c r="G18" s="38" t="n">
+      <c r="G18" s="39" t="n">
         <f aca="false">F18/E18</f>
         <v>58.9170047748603</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="37" t="s">
-        <v>104</v>
+      <c r="A19" s="38" t="s">
+        <v>117</v>
       </c>
       <c r="B19" s="18" t="n">
         <v>1000000</v>
@@ -3889,15 +4509,15 @@
         <f aca="false">CEILING(C19/$B$9,1)</f>
         <v>334</v>
       </c>
-      <c r="E19" s="23" t="n">
+      <c r="E19" s="24" t="n">
         <f aca="false">D19*$B$8</f>
         <v>1667350.4448</v>
       </c>
-      <c r="F19" s="23" t="n">
+      <c r="F19" s="24" t="n">
         <f aca="false">C19*$B$5</f>
         <v>100000000</v>
       </c>
-      <c r="G19" s="38" t="n">
+      <c r="G19" s="39" t="n">
         <f aca="false">F19/E19</f>
         <v>59.9753940821931</v>
       </c>
@@ -3935,7 +4555,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3945,7 +4565,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3955,7 +4575,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -3965,52 +4585,52 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="22" t="n">
+        <v>98</v>
+      </c>
+      <c r="B5" s="23" t="n">
         <f aca="false">Assumptions!$B$29</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="35" t="n">
+        <v>99</v>
+      </c>
+      <c r="B6" s="36" t="n">
         <f aca="false">Assumptions!$B$39</f>
         <v>2.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="36" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" s="37" t="n">
         <f aca="false">'Rent Cost Model'!$D$11</f>
         <v>4160.056</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="23" t="n">
+        <v>101</v>
+      </c>
+      <c r="B8" s="24" t="n">
         <f aca="false">B6*B7</f>
         <v>10400.14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="B9" s="21" t="n">
+        <v>120</v>
+      </c>
+      <c r="B9" s="22" t="n">
         <f aca="false">Assumptions!$B$20</f>
         <v>20000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B10" s="14" t="n">
         <f aca="false">B8/B5</f>
@@ -4019,36 +4639,36 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B11" s="30" t="n">
+        <v>105</v>
+      </c>
+      <c r="B11" s="31" t="n">
         <f aca="false">B10/B9</f>
         <v>0.002080028</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>99</v>
+      <c r="A13" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="s">
-        <v>100</v>
+      <c r="A14" s="38" t="s">
+        <v>113</v>
       </c>
       <c r="B14" s="18" t="n">
         <v>50000</v>
@@ -4057,22 +4677,22 @@
         <f aca="false">CEILING(B14/$B$9,1)</f>
         <v>1</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="24" t="n">
         <f aca="false">C14*$B$8</f>
         <v>10400.14</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="24" t="n">
         <f aca="false">B14*$B$5</f>
         <v>12500</v>
       </c>
-      <c r="F14" s="38" t="n">
+      <c r="F14" s="39" t="n">
         <f aca="false">E14/D14</f>
         <v>1.20190689740715</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37" t="s">
-        <v>101</v>
+      <c r="A15" s="38" t="s">
+        <v>114</v>
       </c>
       <c r="B15" s="18" t="n">
         <v>500000</v>
@@ -4081,22 +4701,22 @@
         <f aca="false">CEILING(B15/$B$9,1)</f>
         <v>1</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="24" t="n">
         <f aca="false">C15*$B$8</f>
         <v>10400.14</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="24" t="n">
         <f aca="false">B15*$B$5</f>
         <v>125000</v>
       </c>
-      <c r="F15" s="38" t="n">
+      <c r="F15" s="39" t="n">
         <f aca="false">E15/D15</f>
         <v>12.0190689740715</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="37" t="s">
-        <v>102</v>
+      <c r="A16" s="38" t="s">
+        <v>115</v>
       </c>
       <c r="B16" s="18" t="n">
         <v>5000000</v>
@@ -4105,22 +4725,22 @@
         <f aca="false">CEILING(B16/$B$9,1)</f>
         <v>1</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="24" t="n">
         <f aca="false">C16*$B$8</f>
         <v>10400.14</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="24" t="n">
         <f aca="false">B16*$B$5</f>
         <v>1250000</v>
       </c>
-      <c r="F16" s="38" t="n">
+      <c r="F16" s="39" t="n">
         <f aca="false">E16/D16</f>
         <v>120.190689740715</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="37" t="s">
-        <v>103</v>
+      <c r="A17" s="38" t="s">
+        <v>116</v>
       </c>
       <c r="B17" s="18" t="n">
         <v>50000000</v>
@@ -4129,22 +4749,22 @@
         <f aca="false">CEILING(B17/$B$9,1)</f>
         <v>3</v>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="24" t="n">
         <f aca="false">C17*$B$8</f>
         <v>31200.42</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="24" t="n">
         <f aca="false">B17*$B$5</f>
         <v>12500000</v>
       </c>
-      <c r="F17" s="38" t="n">
+      <c r="F17" s="39" t="n">
         <f aca="false">E17/D17</f>
         <v>400.63563246905</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="37" t="s">
-        <v>104</v>
+      <c r="A18" s="38" t="s">
+        <v>117</v>
       </c>
       <c r="B18" s="18" t="n">
         <v>500000000</v>
@@ -4153,15 +4773,15 @@
         <f aca="false">CEILING(B18/$B$9,1)</f>
         <v>25</v>
       </c>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="24" t="n">
         <f aca="false">C18*$B$8</f>
         <v>260003.5</v>
       </c>
-      <c r="E18" s="23" t="n">
+      <c r="E18" s="24" t="n">
         <f aca="false">B18*$B$5</f>
         <v>125000000</v>
       </c>
-      <c r="F18" s="38" t="n">
+      <c r="F18" s="39" t="n">
         <f aca="false">E18/D18</f>
         <v>480.76275896286</v>
       </c>
@@ -4203,7 +4823,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4216,7 +4836,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4229,7 +4849,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -4242,7 +4862,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>9100000</v>
@@ -4250,7 +4870,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>0.8</v>
@@ -4258,7 +4878,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B7" s="14" t="n">
         <f aca="false">B5*B6</f>
@@ -4267,61 +4887,61 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B8" s="39" t="n">
+        <v>126</v>
+      </c>
+      <c r="B8" s="40" t="n">
         <f aca="false">Assumptions!$B$31</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="21" t="n">
+        <v>127</v>
+      </c>
+      <c r="B9" s="22" t="n">
         <f aca="false">Assumptions!$B$32</f>
         <v>50</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" s="35" t="n">
+        <v>99</v>
+      </c>
+      <c r="B10" s="36" t="n">
         <f aca="false">Assumptions!$B$40</f>
         <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B11" s="36" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" s="37" t="n">
         <f aca="false">'Rent Cost Model'!$D$11</f>
         <v>4160.056</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B12" s="23" t="n">
+        <v>101</v>
+      </c>
+      <c r="B12" s="24" t="n">
         <f aca="false">B11*B10</f>
         <v>16640.224</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="B13" s="21" t="n">
+        <v>120</v>
+      </c>
+      <c r="B13" s="22" t="n">
         <f aca="false">Assumptions!$B$20</f>
         <v>20000000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B14" s="14" t="n">
         <f aca="false">B12/B8</f>
@@ -4330,7 +4950,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="B15" s="14" t="n">
         <f aca="false">B13/B9</f>
@@ -4339,45 +4959,45 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B16" s="32" t="n">
+        <v>105</v>
+      </c>
+      <c r="B16" s="33" t="n">
         <f aca="false">B14/B15</f>
         <v>0.04160056</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="H18" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="I18" s="20" t="s">
-        <v>119</v>
+      <c r="A18" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="I18" s="21" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="37" t="s">
-        <v>100</v>
+      <c r="A19" s="38" t="s">
+        <v>113</v>
       </c>
       <c r="B19" s="18" t="n">
         <v>7280</v>
@@ -4390,30 +5010,30 @@
         <f aca="false">CEILING(C19/$B$13,1)</f>
         <v>1</v>
       </c>
-      <c r="E19" s="23" t="n">
+      <c r="E19" s="24" t="n">
         <f aca="false">D19*$B$12</f>
         <v>16640.224</v>
       </c>
-      <c r="F19" s="23" t="n">
+      <c r="F19" s="24" t="n">
         <f aca="false">B19*$B$8</f>
         <v>7280</v>
       </c>
-      <c r="G19" s="38" t="n">
+      <c r="G19" s="39" t="n">
         <f aca="false">F19/E19</f>
         <v>0.437494110656203</v>
       </c>
-      <c r="H19" s="23" t="n">
+      <c r="H19" s="24" t="n">
         <f aca="false">F19*12</f>
         <v>87360</v>
       </c>
-      <c r="I19" s="23" t="n">
+      <c r="I19" s="24" t="n">
         <f aca="false">E19*12</f>
         <v>199682.688</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="37" t="s">
-        <v>101</v>
+      <c r="A20" s="38" t="s">
+        <v>114</v>
       </c>
       <c r="B20" s="18" t="n">
         <v>72800</v>
@@ -4426,30 +5046,30 @@
         <f aca="false">CEILING(C20/$B$13,1)</f>
         <v>1</v>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="24" t="n">
         <f aca="false">D20*$B$12</f>
         <v>16640.224</v>
       </c>
-      <c r="F20" s="23" t="n">
+      <c r="F20" s="24" t="n">
         <f aca="false">B20*$B$8</f>
         <v>72800</v>
       </c>
-      <c r="G20" s="38" t="n">
+      <c r="G20" s="39" t="n">
         <f aca="false">F20/E20</f>
         <v>4.37494110656203</v>
       </c>
-      <c r="H20" s="23" t="n">
+      <c r="H20" s="24" t="n">
         <f aca="false">F20*12</f>
         <v>873600</v>
       </c>
-      <c r="I20" s="23" t="n">
+      <c r="I20" s="24" t="n">
         <f aca="false">E20*12</f>
         <v>199682.688</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="37" t="s">
-        <v>102</v>
+      <c r="A21" s="38" t="s">
+        <v>115</v>
       </c>
       <c r="B21" s="18" t="n">
         <v>728000</v>
@@ -4462,30 +5082,30 @@
         <f aca="false">CEILING(C21/$B$13,1)</f>
         <v>2</v>
       </c>
-      <c r="E21" s="23" t="n">
+      <c r="E21" s="24" t="n">
         <f aca="false">D21*$B$12</f>
         <v>33280.448</v>
       </c>
-      <c r="F21" s="23" t="n">
+      <c r="F21" s="24" t="n">
         <f aca="false">B21*$B$8</f>
         <v>728000</v>
       </c>
-      <c r="G21" s="38" t="n">
+      <c r="G21" s="39" t="n">
         <f aca="false">F21/E21</f>
         <v>21.8747055328101</v>
       </c>
-      <c r="H21" s="23" t="n">
+      <c r="H21" s="24" t="n">
         <f aca="false">F21*12</f>
         <v>8736000</v>
       </c>
-      <c r="I21" s="23" t="n">
+      <c r="I21" s="24" t="n">
         <f aca="false">E21*12</f>
         <v>399365.376</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="37" t="s">
-        <v>103</v>
+      <c r="A22" s="38" t="s">
+        <v>116</v>
       </c>
       <c r="B22" s="14" t="n">
         <f aca="false">$B$7</f>
@@ -4499,30 +5119,30 @@
         <f aca="false">CEILING(C22/$B$13,1)</f>
         <v>19</v>
       </c>
-      <c r="E22" s="23" t="n">
+      <c r="E22" s="24" t="n">
         <f aca="false">D22*$B$12</f>
         <v>316164.256</v>
       </c>
-      <c r="F22" s="23" t="n">
+      <c r="F22" s="24" t="n">
         <f aca="false">B22*$B$8</f>
         <v>7280000</v>
       </c>
-      <c r="G22" s="38" t="n">
+      <c r="G22" s="39" t="n">
         <f aca="false">F22/E22</f>
         <v>23.0260058240107</v>
       </c>
-      <c r="H22" s="23" t="n">
+      <c r="H22" s="24" t="n">
         <f aca="false">F22*12</f>
         <v>87360000</v>
       </c>
-      <c r="I22" s="23" t="n">
+      <c r="I22" s="24" t="n">
         <f aca="false">E22*12</f>
         <v>3793971.072</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="37" t="s">
-        <v>104</v>
+      <c r="A23" s="38" t="s">
+        <v>117</v>
       </c>
       <c r="B23" s="14" t="n">
         <f aca="false">$B$7</f>
@@ -4536,30 +5156,30 @@
         <f aca="false">CEILING(C23/$B$13,1)</f>
         <v>19</v>
       </c>
-      <c r="E23" s="23" t="n">
+      <c r="E23" s="24" t="n">
         <f aca="false">D23*$B$12</f>
         <v>316164.256</v>
       </c>
-      <c r="F23" s="23" t="n">
+      <c r="F23" s="24" t="n">
         <f aca="false">B23*$B$8</f>
         <v>7280000</v>
       </c>
-      <c r="G23" s="38" t="n">
+      <c r="G23" s="39" t="n">
         <f aca="false">F23/E23</f>
         <v>23.0260058240107</v>
       </c>
-      <c r="H23" s="23" t="n">
+      <c r="H23" s="24" t="n">
         <f aca="false">F23*12</f>
         <v>87360000</v>
       </c>
-      <c r="I23" s="23" t="n">
+      <c r="I23" s="24" t="n">
         <f aca="false">E23*12</f>
         <v>3793971.072</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="37" t="s">
-        <v>120</v>
+      <c r="A24" s="38" t="s">
+        <v>133</v>
       </c>
       <c r="B24" s="14" t="n">
         <f aca="false">$B$7</f>
@@ -4573,30 +5193,30 @@
         <f aca="false">CEILING(C24/$B$13,1)</f>
         <v>19</v>
       </c>
-      <c r="E24" s="23" t="n">
+      <c r="E24" s="24" t="n">
         <f aca="false">D24*$B$12</f>
         <v>316164.256</v>
       </c>
-      <c r="F24" s="23" t="n">
+      <c r="F24" s="24" t="n">
         <f aca="false">B24*$B$8</f>
         <v>7280000</v>
       </c>
-      <c r="G24" s="38" t="n">
+      <c r="G24" s="39" t="n">
         <f aca="false">F24/E24</f>
         <v>23.0260058240107</v>
       </c>
-      <c r="H24" s="23" t="n">
+      <c r="H24" s="24" t="n">
         <f aca="false">F24*12</f>
         <v>87360000</v>
       </c>
-      <c r="I24" s="23" t="n">
+      <c r="I24" s="24" t="n">
         <f aca="false">E24*12</f>
         <v>3793971.072</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="37" t="s">
-        <v>121</v>
+      <c r="A25" s="38" t="s">
+        <v>134</v>
       </c>
       <c r="B25" s="14" t="n">
         <f aca="false">$B$7</f>
@@ -4610,30 +5230,30 @@
         <f aca="false">CEILING(C25/$B$13,1)</f>
         <v>19</v>
       </c>
-      <c r="E25" s="23" t="n">
+      <c r="E25" s="24" t="n">
         <f aca="false">D25*$B$12</f>
         <v>316164.256</v>
       </c>
-      <c r="F25" s="23" t="n">
+      <c r="F25" s="24" t="n">
         <f aca="false">B25*$B$8</f>
         <v>7280000</v>
       </c>
-      <c r="G25" s="38" t="n">
+      <c r="G25" s="39" t="n">
         <f aca="false">F25/E25</f>
         <v>23.0260058240107</v>
       </c>
-      <c r="H25" s="23" t="n">
+      <c r="H25" s="24" t="n">
         <f aca="false">F25*12</f>
         <v>87360000</v>
       </c>
-      <c r="I25" s="23" t="n">
+      <c r="I25" s="24" t="n">
         <f aca="false">E25*12</f>
         <v>3793971.072</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="37" t="s">
-        <v>122</v>
+      <c r="A26" s="38" t="s">
+        <v>135</v>
       </c>
       <c r="B26" s="14" t="n">
         <f aca="false">$B$7</f>
@@ -4647,30 +5267,30 @@
         <f aca="false">CEILING(C26/$B$13,1)</f>
         <v>19</v>
       </c>
-      <c r="E26" s="23" t="n">
+      <c r="E26" s="24" t="n">
         <f aca="false">D26*$B$12</f>
         <v>316164.256</v>
       </c>
-      <c r="F26" s="23" t="n">
+      <c r="F26" s="24" t="n">
         <f aca="false">B26*$B$8</f>
         <v>7280000</v>
       </c>
-      <c r="G26" s="38" t="n">
+      <c r="G26" s="39" t="n">
         <f aca="false">F26/E26</f>
         <v>23.0260058240107</v>
       </c>
-      <c r="H26" s="23" t="n">
+      <c r="H26" s="24" t="n">
         <f aca="false">F26*12</f>
         <v>87360000</v>
       </c>
-      <c r="I26" s="23" t="n">
+      <c r="I26" s="24" t="n">
         <f aca="false">E26*12</f>
         <v>3793971.072</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="37" t="s">
-        <v>123</v>
+      <c r="A27" s="38" t="s">
+        <v>136</v>
       </c>
       <c r="B27" s="14" t="n">
         <f aca="false">$B$7</f>
@@ -4684,30 +5304,30 @@
         <f aca="false">CEILING(C27/$B$13,1)</f>
         <v>19</v>
       </c>
-      <c r="E27" s="23" t="n">
+      <c r="E27" s="24" t="n">
         <f aca="false">D27*$B$12</f>
         <v>316164.256</v>
       </c>
-      <c r="F27" s="23" t="n">
+      <c r="F27" s="24" t="n">
         <f aca="false">B27*$B$8</f>
         <v>7280000</v>
       </c>
-      <c r="G27" s="38" t="n">
+      <c r="G27" s="39" t="n">
         <f aca="false">F27/E27</f>
         <v>23.0260058240107</v>
       </c>
-      <c r="H27" s="23" t="n">
+      <c r="H27" s="24" t="n">
         <f aca="false">F27*12</f>
         <v>87360000</v>
       </c>
-      <c r="I27" s="23" t="n">
+      <c r="I27" s="24" t="n">
         <f aca="false">E27*12</f>
         <v>3793971.072</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="37" t="s">
-        <v>124</v>
+      <c r="A28" s="38" t="s">
+        <v>137</v>
       </c>
       <c r="B28" s="14" t="n">
         <f aca="false">$B$7</f>
@@ -4721,36 +5341,36 @@
         <f aca="false">CEILING(C28/$B$13,1)</f>
         <v>19</v>
       </c>
-      <c r="E28" s="23" t="n">
+      <c r="E28" s="24" t="n">
         <f aca="false">D28*$B$12</f>
         <v>316164.256</v>
       </c>
-      <c r="F28" s="23" t="n">
+      <c r="F28" s="24" t="n">
         <f aca="false">B28*$B$8</f>
         <v>7280000</v>
       </c>
-      <c r="G28" s="38" t="n">
+      <c r="G28" s="39" t="n">
         <f aca="false">F28/E28</f>
         <v>23.0260058240107</v>
       </c>
-      <c r="H28" s="23" t="n">
+      <c r="H28" s="24" t="n">
         <f aca="false">F28*12</f>
         <v>87360000</v>
       </c>
-      <c r="I28" s="23" t="n">
+      <c r="I28" s="24" t="n">
         <f aca="false">E28*12</f>
         <v>3793971.072</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="H29" s="25" t="n">
+      <c r="A29" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="H29" s="26" t="n">
         <f aca="false">SUM(H19:H28)</f>
         <v>621216960</v>
       </c>
-      <c r="I29" s="25" t="n">
+      <c r="I29" s="26" t="n">
         <f aca="false">SUM(I19:I28)</f>
         <v>27356528.256</v>
       </c>
@@ -4788,7 +5408,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4796,7 +5416,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4804,7 +5424,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -4812,7 +5432,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>10</v>
@@ -4820,7 +5440,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>1000000</v>
@@ -4828,7 +5448,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B7" s="18" t="n">
         <v>10</v>
@@ -4836,7 +5456,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="B8" s="14" t="n">
         <f aca="false">B5*B6*B7</f>
@@ -4845,34 +5465,34 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" s="31" t="n">
+        <v>145</v>
+      </c>
+      <c r="B9" s="32" t="n">
         <f aca="false">Assumptions!$B$30</f>
         <v>0.0003</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="36" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" s="37" t="n">
         <f aca="false">'Rent Cost Model'!$D$11</f>
         <v>4160.056</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B11" s="21" t="n">
+        <v>102</v>
+      </c>
+      <c r="B11" s="22" t="n">
         <f aca="false">Assumptions!$B$19</f>
         <v>30000000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="B12" s="14" t="n">
         <f aca="false">CEILING(B8/B11,1)</f>
@@ -4881,57 +5501,57 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B13" s="23" t="n">
+        <v>147</v>
+      </c>
+      <c r="B13" s="24" t="n">
         <f aca="false">B12*B10</f>
         <v>16640.224</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B14" s="34" t="n">
+        <v>148</v>
+      </c>
+      <c r="B14" s="35" t="n">
         <f aca="false">B13/B8</f>
         <v>0.00016640224</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>99</v>
+      <c r="A17" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="n">
         <v>0.0001</v>
       </c>
-      <c r="B18" s="23" t="n">
+      <c r="B18" s="24" t="n">
         <f aca="false">$B$8*A18</f>
         <v>10000</v>
       </c>
-      <c r="C18" s="23" t="n">
+      <c r="C18" s="24" t="n">
         <f aca="false">$B$13</f>
         <v>16640.224</v>
       </c>
-      <c r="D18" s="38" t="n">
+      <c r="D18" s="39" t="n">
         <f aca="false">B18/C18</f>
         <v>0.600953448703575</v>
       </c>
@@ -4940,15 +5560,15 @@
       <c r="A19" s="17" t="n">
         <v>0.000166</v>
       </c>
-      <c r="B19" s="23" t="n">
+      <c r="B19" s="24" t="n">
         <f aca="false">$B$8*A19</f>
         <v>16600</v>
       </c>
-      <c r="C19" s="23" t="n">
+      <c r="C19" s="24" t="n">
         <f aca="false">$B$13</f>
         <v>16640.224</v>
       </c>
-      <c r="D19" s="38" t="n">
+      <c r="D19" s="39" t="n">
         <f aca="false">B19/C19</f>
         <v>0.997582724847935</v>
       </c>
@@ -4957,15 +5577,15 @@
       <c r="A20" s="17" t="n">
         <v>0.0003</v>
       </c>
-      <c r="B20" s="23" t="n">
+      <c r="B20" s="24" t="n">
         <f aca="false">$B$8*A20</f>
         <v>30000</v>
       </c>
-      <c r="C20" s="23" t="n">
+      <c r="C20" s="24" t="n">
         <f aca="false">$B$13</f>
         <v>16640.224</v>
       </c>
-      <c r="D20" s="38" t="n">
+      <c r="D20" s="39" t="n">
         <f aca="false">B20/C20</f>
         <v>1.80286034611073</v>
       </c>
@@ -4974,22 +5594,22 @@
       <c r="A21" s="17" t="n">
         <v>0.001</v>
       </c>
-      <c r="B21" s="23" t="n">
+      <c r="B21" s="24" t="n">
         <f aca="false">$B$8*A21</f>
         <v>100000</v>
       </c>
-      <c r="C21" s="23" t="n">
+      <c r="C21" s="24" t="n">
         <f aca="false">$B$13</f>
         <v>16640.224</v>
       </c>
-      <c r="D21" s="38" t="n">
+      <c r="D21" s="39" t="n">
         <f aca="false">B21/C21</f>
         <v>6.00953448703575</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -4997,7 +5617,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B24" s="18" t="n">
         <v>100</v>
@@ -5005,7 +5625,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="B25" s="14" t="n">
         <f aca="false">B8/B24</f>
@@ -5014,7 +5634,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B26" s="14" t="n">
         <f aca="false">CEILING(B25/B11,1)</f>
@@ -5023,16 +5643,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="B27" s="23" t="n">
+        <v>155</v>
+      </c>
+      <c r="B27" s="24" t="n">
         <f aca="false">B26*B10</f>
         <v>4160.056</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="B28" s="11" t="n">
         <v>0.03</v>
@@ -5040,18 +5660,18 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="B29" s="23" t="n">
+        <v>157</v>
+      </c>
+      <c r="B29" s="24" t="n">
         <f aca="false">B25*B28</f>
         <v>30000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B30" s="38" t="n">
+        <v>158</v>
+      </c>
+      <c r="B30" s="39" t="n">
         <f aca="false">B29/B27</f>
         <v>7.2114413844429</v>
       </c>
@@ -5093,7 +5713,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5105,7 +5725,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5117,7 +5737,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -5129,87 +5749,87 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B5" s="31" t="n">
+        <v>161</v>
+      </c>
+      <c r="B5" s="32" t="n">
         <f aca="false">'Rent Cost Model'!$D$13</f>
         <v>0.000138668533333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B6" s="39" t="n">
+        <v>162</v>
+      </c>
+      <c r="B6" s="40" t="n">
         <f aca="false">Assumptions!$B$24</f>
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="B7" s="22" t="n">
+        <v>163</v>
+      </c>
+      <c r="B7" s="23" t="n">
         <f aca="false">Assumptions!$B$25</f>
         <v>0.003</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="B8" s="40" t="n">
+        <v>164</v>
+      </c>
+      <c r="B8" s="41" t="n">
         <f aca="false">B7/B5</f>
         <v>21.6343241533287</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="21" t="n">
+        <v>102</v>
+      </c>
+      <c r="B9" s="22" t="n">
         <f aca="false">Assumptions!$B$19</f>
         <v>30000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="36" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" s="37" t="n">
         <f aca="false">'Rent Cost Model'!$D$11</f>
         <v>4160.056</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="H12" s="20" t="s">
-        <v>158</v>
+      <c r="A12" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>1800000000</v>
@@ -5221,7 +5841,7 @@
         <f aca="false">CEILING(C13/$B$9,1)</f>
         <v>120000</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="24" t="n">
         <f aca="false">D13*$B$10</f>
         <v>499206720</v>
       </c>
@@ -5233,14 +5853,14 @@
         <f aca="false">F13*$B$5</f>
         <v>0.277337066666667</v>
       </c>
-      <c r="H13" s="40" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">(G13/$B$7)/30</f>
         <v>3.08152296296296</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="B14" s="18" t="n">
         <v>2000000000</v>
@@ -5252,7 +5872,7 @@
         <f aca="false">CEILING(C14/$B$9,1)</f>
         <v>100000</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="24" t="n">
         <f aca="false">D14*$B$10</f>
         <v>416005600</v>
       </c>
@@ -5264,14 +5884,14 @@
         <f aca="false">F14*$B$5</f>
         <v>0.2080028</v>
       </c>
-      <c r="H14" s="40" t="n">
+      <c r="H14" s="41" t="n">
         <f aca="false">(G14/$B$7)/30</f>
         <v>2.31114222222222</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="B15" s="18" t="n">
         <v>3000000000</v>
@@ -5283,7 +5903,7 @@
         <f aca="false">CEILING(C15/$B$9,1)</f>
         <v>20000</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="24" t="n">
         <f aca="false">D15*$B$10</f>
         <v>83201120</v>
       </c>
@@ -5295,14 +5915,14 @@
         <f aca="false">F15*$B$5</f>
         <v>0.0277337066666667</v>
       </c>
-      <c r="H15" s="40" t="n">
+      <c r="H15" s="41" t="n">
         <f aca="false">(G15/$B$7)/30</f>
         <v>0.308152296296296</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -5314,7 +5934,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>0.01</v>
@@ -5322,7 +5942,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="B19" s="14" t="n">
         <f aca="false">B13*B18</f>
@@ -5331,7 +5951,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="B20" s="14" t="n">
         <f aca="false">C13*B18</f>
@@ -5340,7 +5960,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B21" s="14" t="n">
         <f aca="false">CEILING(B20/B9,1)</f>
@@ -5349,16 +5969,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="B22" s="23" t="n">
+        <v>180</v>
+      </c>
+      <c r="B22" s="24" t="n">
         <f aca="false">B21*B10</f>
         <v>4992067.2</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B23" s="17" t="n">
         <v>2E-005</v>
@@ -5366,9 +5986,9 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="B24" s="23" t="n">
+        <v>182</v>
+      </c>
+      <c r="B24" s="24" t="n">
         <f aca="false">C13*B23</f>
         <v>72000000</v>
       </c>
